--- a/population/inputs/age_groups_by_data_source.xlsx
+++ b/population/inputs/age_groups_by_data_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a43f8f3820cb67c/ICLUS_v3/population/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{88DF4B41-B40C-4543-AD3C-BE9BE006CB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D3D0E28-1CD1-4CA4-98F2-9A324D9960E5}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{88DF4B41-B40C-4543-AD3C-BE9BE006CB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A18649E-22DB-4161-ABCC-BC87A119D967}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E8756FC9-B9AE-47B0-AFD1-208DB6212047}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E8756FC9-B9AE-47B0-AFD1-208DB6212047}"/>
   </bookViews>
   <sheets>
     <sheet name="Age groups" sheetId="1" r:id="rId1"/>
@@ -410,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -418,85 +418,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -832,19 +818,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5244ED3C-87D5-413E-982A-759B8ACF2927}">
-  <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="16.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultColWidth="16.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="21.88671875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="22.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="16.88671875" style="4"/>
+    <col min="1" max="1" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="21.90625" customWidth="1"/>
+    <col min="6" max="6" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="20" t="s">
@@ -855,582 +840,578 @@
         <v>41</v>
       </c>
       <c r="E1" s="23"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="26" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24" t="s">
+    <row r="2" spans="1:8" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="25"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="8" t="s">
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="12"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="7"/>
+      <c r="B3" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="G3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="7" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="16"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="7" t="s">
+      <c r="F5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="H5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="18" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="7" t="s">
+      <c r="F6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="G6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="H6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="7" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="16"/>
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="G7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="H7" s="15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="H8" s="15"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="16"/>
+      <c r="E9" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="7">
+      <c r="G9" s="3">
         <v>20</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="H9" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="7">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="3">
         <v>21</v>
       </c>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="7" t="s">
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="10"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8" t="s">
+      <c r="F12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="H12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="7" t="s">
+      <c r="D13" s="16"/>
+      <c r="E13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="7" t="s">
+      <c r="F13" s="16"/>
+      <c r="G13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="H13" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="8" t="s">
+      <c r="F14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="H14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="7" t="s">
+      <c r="D15" s="16"/>
+      <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="7" t="s">
+      <c r="F15" s="16"/>
+      <c r="G15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="H15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="8" t="s">
+      <c r="F16" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="G16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="H16" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="7" t="s">
+      <c r="D17" s="16"/>
+      <c r="E17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="7" t="s">
+      <c r="F17" s="16"/>
+      <c r="G17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="H17" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="8" t="s">
+      <c r="B18" s="16"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7" t="s">
+      <c r="F18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="G18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="H18" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8" t="s">
+      <c r="B19" s="16"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="8" t="s">
+      <c r="F19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="G19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="H19" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="7" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="H20" s="15"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="8" t="s">
+      <c r="B21" s="16"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="8" t="s">
+      <c r="F21" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="G21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="H21" s="15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="7" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="10"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+      <c r="H22" s="15"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="7" t="s">
+      <c r="B23" s="16"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="7" t="s">
+      <c r="F23" s="16"/>
+      <c r="G23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="H23" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="8" t="s">
+      <c r="B24" s="16"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="8" t="s">
+      <c r="F24" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="G24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="H24" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="7" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="7" t="s">
+      <c r="F25" s="16"/>
+      <c r="G25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="H25" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="8" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="10" t="s">
+      <c r="F26" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="G26" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="H26" s="15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="7" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="10"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="7" t="s">
+      <c r="F27" s="15"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="15"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="10"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="7" t="s">
+      <c r="F28" s="15"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="15"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="10"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="I26:I29"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H11"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="D12:D13"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="C9:C11"/>
@@ -1439,38 +1420,13 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="D26:D29"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F26:F29"/>
     <mergeCell ref="G26:G29"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1480,36 +1436,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228FE9F1-8D75-4271-B8F9-9F501E6DC280}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="26.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="11" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>54</v>
       </c>
@@ -1529,7 +1485,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>55</v>
       </c>
@@ -1549,7 +1505,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>56</v>
       </c>
@@ -1569,8 +1525,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="24" t="s">
         <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1589,15 +1545,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="24"/>
       <c r="B6" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -1607,15 +1563,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="24"/>
       <c r="B7" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="2" t="s">
         <v>67</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -1625,9 +1581,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="E8" s="29" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="24"/>
+      <c r="E8" s="2" t="s">
         <v>68</v>
       </c>
       <c r="F8" s="2" t="s">

--- a/population/inputs/age_groups_by_data_source.xlsx
+++ b/population/inputs/age_groups_by_data_source.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a43f8f3820cb67c/ICLUS_v3/population/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{88DF4B41-B40C-4543-AD3C-BE9BE006CB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A18649E-22DB-4161-ABCC-BC87A119D967}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="8_{88DF4B41-B40C-4543-AD3C-BE9BE006CB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2186D601-76C1-48CC-8A16-63A7EA93F8C4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E8756FC9-B9AE-47B0-AFD1-208DB6212047}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E8756FC9-B9AE-47B0-AFD1-208DB6212047}"/>
   </bookViews>
   <sheets>
     <sheet name="Age groups" sheetId="1" r:id="rId1"/>
     <sheet name="Race" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="82">
   <si>
     <t>1 to 4</t>
   </si>
@@ -247,13 +248,49 @@
   </si>
   <si>
     <t>Some Other Race alone</t>
+  </si>
+  <si>
+    <t>57059-2025-09-Demographic-Projections</t>
+  </si>
+  <si>
+    <t>2. Pop by age, sex, marital</t>
+  </si>
+  <si>
+    <t>3. Immig by age, sex, status</t>
+  </si>
+  <si>
+    <t>5. Mort rates by age, sex</t>
+  </si>
+  <si>
+    <t>6. Fert rates by age, birthplace</t>
+  </si>
+  <si>
+    <t>CSV files</t>
+  </si>
+  <si>
+    <t>grossMigration_byYearAgeSexStatusFlow</t>
+  </si>
+  <si>
+    <t>mortalityRates_byYearAgeSex</t>
+  </si>
+  <si>
+    <t>fertilityRates_byYearAgePlace</t>
+  </si>
+  <si>
+    <t>CDC Wonder</t>
+  </si>
+  <si>
+    <t>Births</t>
+  </si>
+  <si>
+    <t>Mortality</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,8 +304,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -293,8 +337,62 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -406,11 +504,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -454,12 +570,24 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -469,21 +597,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,6 +645,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -819,27 +969,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5244ED3C-87D5-413E-982A-759B8ACF2927}">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="16.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="16.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="21.90625" customWidth="1"/>
-    <col min="6" max="6" width="22.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="21.88671875" customWidth="1"/>
+    <col min="6" max="6" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="22" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="23"/>
+      <c r="E1" s="19"/>
       <c r="F1" s="3" t="s">
         <v>20</v>
       </c>
@@ -850,7 +1000,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11"/>
       <c r="B2" s="11" t="s">
         <v>50</v>
@@ -868,12 +1018,12 @@
       <c r="G2" s="11"/>
       <c r="H2" s="12"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -882,39 +1032,39 @@
       <c r="E3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="15" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="18"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="22"/>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="16" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="15" t="s">
         <v>43</v>
       </c>
       <c r="E5" s="8" t="s">
@@ -930,11 +1080,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="16"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="15"/>
       <c r="E6" s="8" t="s">
         <v>4</v>
       </c>
@@ -948,95 +1098,95 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="15"/>
       <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>5</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="20" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
       <c r="G8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
+      <c r="H8" s="20"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16" t="s">
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="15" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="3">
         <v>20</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="20" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
       <c r="G10" s="3">
         <v>21</v>
       </c>
-      <c r="H10" s="15"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="H10" s="20"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
       <c r="G11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="15"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H11" s="20"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1046,13 +1196,13 @@
       <c r="C12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="15" t="s">
         <v>21</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -1062,7 +1212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
@@ -1072,11 +1222,11 @@
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="16"/>
+      <c r="D13" s="15"/>
       <c r="E13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="16"/>
+      <c r="F13" s="15"/>
       <c r="G13" s="3" t="s">
         <v>9</v>
       </c>
@@ -1084,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1094,13 +1244,13 @@
       <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="15" t="s">
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -1110,7 +1260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1120,11 +1270,11 @@
       <c r="C15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="16"/>
+      <c r="D15" s="15"/>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="16"/>
+      <c r="F15" s="15"/>
       <c r="G15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1132,7 +1282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
@@ -1142,13 +1292,13 @@
       <c r="C16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -1158,21 +1308,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="16"/>
+      <c r="D17" s="15"/>
       <c r="E17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="16"/>
+      <c r="F17" s="15"/>
       <c r="G17" s="3" t="s">
         <v>13</v>
       </c>
@@ -1180,13 +1330,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="16" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="15" t="s">
         <v>45</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -1202,83 +1352,83 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="16" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16" t="s">
+      <c r="B19" s="15"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="15" t="s">
         <v>15</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
       <c r="G20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="15"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="16" t="s">
+      <c r="H20" s="20"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="16" t="s">
+      <c r="B21" s="15"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="15" t="s">
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
       <c r="G22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="15"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H22" s="20"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="16"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="15"/>
       <c r="E23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F23" s="16"/>
+      <c r="F23" s="15"/>
       <c r="G23" s="3" t="s">
         <v>17</v>
       </c>
@@ -1286,19 +1436,19 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="16" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="16" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="15" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="15" t="s">
         <v>25</v>
       </c>
       <c r="G24" s="3" t="s">
@@ -1308,15 +1458,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="16"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="15"/>
       <c r="E25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F25" s="16"/>
+      <c r="F25" s="15"/>
       <c r="G25" s="3" t="s">
         <v>34</v>
       </c>
@@ -1324,73 +1474,77 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="16" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="15" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="H26" s="20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="16"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="15"/>
       <c r="E27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="15"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="16"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="20"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="15"/>
       <c r="E28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="15"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="16"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="20"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="15"/>
       <c r="E29" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="15"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="G26:G29"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="A24:A29"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="H9:H11"/>
@@ -1407,11 +1561,15 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F16:F17"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="C9:C11"/>
@@ -1419,14 +1577,6 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="D24:D25"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="G26:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1436,15 +1586,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228FE9F1-8D75-4271-B8F9-9F501E6DC280}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="26.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
@@ -1465,7 +1615,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>54</v>
       </c>
@@ -1485,7 +1635,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>55</v>
       </c>
@@ -1505,7 +1655,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>56</v>
       </c>
@@ -1525,7 +1675,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>57</v>
       </c>
@@ -1545,7 +1695,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="24"/>
       <c r="B6" s="2" t="s">
         <v>61</v>
@@ -1563,7 +1713,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="24"/>
       <c r="B7" s="2" t="s">
         <v>63</v>
@@ -1581,7 +1731,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="24"/>
       <c r="E8" s="2" t="s">
         <v>68</v>
@@ -1597,4 +1747,235 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFB2515-09F6-4F4E-8048-6D78A72C721A}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" s="30"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" s="45" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2007</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="27"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="27"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2021</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="27"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2022</v>
+      </c>
+      <c r="B7" s="26"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="27"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="27"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2023</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="27"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="27"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="26"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="27"/>
+      <c r="I9" s="28"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="28"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="26"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="28"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="26"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="28"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="26"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="28"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="26"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="28"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="26"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="28"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="26"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="28"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="26"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="28"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2098</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/population/inputs/age_groups_by_data_source.xlsx
+++ b/population/inputs/age_groups_by_data_source.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a43f8f3820cb67c/ICLUS_v3/population/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="8_{88DF4B41-B40C-4543-AD3C-BE9BE006CB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2186D601-76C1-48CC-8A16-63A7EA93F8C4}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="8_{88DF4B41-B40C-4543-AD3C-BE9BE006CB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53EEC357-34F3-445E-9DC8-4C7BF3455B19}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E8756FC9-B9AE-47B0-AFD1-208DB6212047}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{E8756FC9-B9AE-47B0-AFD1-208DB6212047}"/>
   </bookViews>
   <sheets>
     <sheet name="Age groups" sheetId="1" r:id="rId1"/>
     <sheet name="Race" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Migration data points since 200" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="94">
   <si>
     <t>1 to 4</t>
   </si>
@@ -284,6 +285,42 @@
   </si>
   <si>
     <t>Mortality</t>
+  </si>
+  <si>
+    <t>Census (Decennial)</t>
+  </si>
+  <si>
+    <t>Census (Intercensal)</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>1990, 2000</t>
+  </si>
+  <si>
+    <t>2010-2024</t>
+  </si>
+  <si>
+    <t>ACS</t>
+  </si>
+  <si>
+    <t>Net Migration</t>
+  </si>
+  <si>
+    <t>County-to-county</t>
+  </si>
+  <si>
+    <t>State-to-county</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>2006-2020</t>
+  </si>
+  <si>
+    <t>2018-2022</t>
   </si>
 </sst>
 </file>
@@ -526,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -570,66 +607,60 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -982,14 +1013,14 @@
       <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="18" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="19"/>
+      <c r="E1" s="35"/>
       <c r="F1" s="3" t="s">
         <v>20</v>
       </c>
@@ -1020,10 +1051,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="36" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -1032,13 +1063,13 @@
       <c r="E3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="30" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1046,25 +1077,25 @@
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="22"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="37"/>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="15" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="30" t="s">
         <v>43</v>
       </c>
       <c r="E5" s="8" t="s">
@@ -1081,10 +1112,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="15"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="8" t="s">
         <v>4</v>
       </c>
@@ -1099,26 +1130,26 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
+      <c r="A7" s="30"/>
       <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="30" t="s">
         <v>5</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="31" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1129,62 +1160,62 @@
       <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
       <c r="G8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="20"/>
+      <c r="H8" s="31"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15" t="s">
+      <c r="D9" s="30"/>
+      <c r="E9" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="30" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="3">
         <v>20</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="31" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
       <c r="G10" s="3">
         <v>21</v>
       </c>
-      <c r="H10" s="20"/>
+      <c r="H10" s="31"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="20"/>
+      <c r="H11" s="31"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -1196,13 +1227,13 @@
       <c r="C12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="30" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="30" t="s">
         <v>21</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -1222,11 +1253,11 @@
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="15"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="15"/>
+      <c r="F13" s="30"/>
       <c r="G13" s="3" t="s">
         <v>9</v>
       </c>
@@ -1244,13 +1275,13 @@
       <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="30" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="30" t="s">
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -1270,11 +1301,11 @@
       <c r="C15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="15"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="15"/>
+      <c r="F15" s="30"/>
       <c r="G15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1292,13 +1323,13 @@
       <c r="C16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="30" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="30" t="s">
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -1312,17 +1343,17 @@
       <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="15"/>
+      <c r="D17" s="30"/>
       <c r="E17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="15"/>
+      <c r="F17" s="30"/>
       <c r="G17" s="3" t="s">
         <v>13</v>
       </c>
@@ -1334,9 +1365,9 @@
       <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="15" t="s">
+      <c r="B18" s="30"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="30" t="s">
         <v>45</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -1353,82 +1384,82 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15" t="s">
+      <c r="B19" s="30"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="H19" s="31" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
       <c r="G20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="20"/>
+      <c r="H20" s="31"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="15" t="s">
+      <c r="B21" s="30"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="30" t="s">
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="20" t="s">
+      <c r="H21" s="31" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
       <c r="G22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="20"/>
+      <c r="H22" s="31"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="15"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="30"/>
       <c r="E23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F23" s="15"/>
+      <c r="F23" s="30"/>
       <c r="G23" s="3" t="s">
         <v>17</v>
       </c>
@@ -1437,18 +1468,18 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="15" t="s">
+      <c r="B24" s="30"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="30" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="30" t="s">
         <v>25</v>
       </c>
       <c r="G24" s="3" t="s">
@@ -1459,14 +1490,14 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="15"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F25" s="15"/>
+      <c r="F25" s="30"/>
       <c r="G25" s="3" t="s">
         <v>34</v>
       </c>
@@ -1475,76 +1506,79 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="15" t="s">
+      <c r="A26" s="30"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="30" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="20" t="s">
+      <c r="H26" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="15"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="20"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="20"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="31"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="15"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="20"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="31"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="15"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="20"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="G26:G29"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C29"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="D24:D25"/>
     <mergeCell ref="A24:A29"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="H9:H11"/>
@@ -1561,22 +1595,19 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="F19:F20"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C29"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="G26:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1676,7 +1707,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1696,7 +1727,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="24"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="2" t="s">
         <v>61</v>
       </c>
@@ -1714,7 +1745,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="2" t="s">
         <v>63</v>
       </c>
@@ -1732,7 +1763,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
+      <c r="A8" s="39"/>
       <c r="E8" s="2" t="s">
         <v>68</v>
       </c>
@@ -1766,209 +1797,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="31" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="30" t="s">
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="30"/>
+      <c r="J1" s="42"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="44" t="s">
+      <c r="E2" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="28" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2007</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="27"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="16"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="27"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="16"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2021</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="27"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="16"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2022</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="27"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="27"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="16"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="16"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2023</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="27"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="27"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="16"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2024</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="27"/>
-      <c r="I9" s="28"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="16"/>
+      <c r="I9" s="17"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2025</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="28"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="26"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="28"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="26"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="28"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="26"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="28"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="26"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="28"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="17"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="26"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="28"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="26"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="28"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="26"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2098</v>
       </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="40"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1978,4 +1998,88 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C94441-6429-4091-B0AE-49DCA317851E}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>